--- a/media/exports/reports/2026-01/cost-to-win.xlsx
+++ b/media/exports/reports/2026-01/cost-to-win.xlsx
@@ -23,44 +23,53 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;[Red](#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
@@ -93,31 +102,31 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -640,8 +649,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 cost-to-win.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-win.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -880,8 +889,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 cost-to-win.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-win.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1312,8 +1321,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 cost-to-win.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-win.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-01/cost-to-win.xlsx
+++ b/media/exports/reports/2026-01/cost-to-win.xlsx
@@ -12,7 +12,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="January_2026">'Report'!$B$8</definedName>
+    <definedName name="January_last_year">'Report'!$B$9</definedName>
+    <definedName name="Year_to_date_Jul_to_Jan_2026">'Report'!$B$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -118,7 +124,9 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -204,6 +212,150 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Marketing spend by month</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Marketing spend</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$A$6:$A$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$C$6:$C$21</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="cost_to_win_Data" displayName="cost_to_win_Data" ref="A5:E21" headerRowCount="1">
+  <autoFilter ref="A5:E21"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Month"/>
+    <tableColumn id="2" name="Status"/>
+    <tableColumn id="3" name="Marketing spend"/>
+    <tableColumn id="4" name="New customers"/>
+    <tableColumn id="5" name="Cost per new customer"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -514,14 +666,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -650,7 +802,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-win.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-win.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -684,14 +836,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -890,7 +1042,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-win.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-win.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -925,14 +1077,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1322,11 +1474,15 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-win.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-win.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/media/exports/reports/2026-01/cost-to-win.xlsx
+++ b/media/exports/reports/2026-01/cost-to-win.xlsx
@@ -12,10 +12,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="January_2026">'Report'!$B$8</definedName>
-    <definedName name="January_last_year">'Report'!$B$9</definedName>
-    <definedName name="Year_to_date_Jul_to_Jan_2026">'Report'!$B$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$18</definedName>
+    <definedName name="January_2026">'Report'!$B$9</definedName>
+    <definedName name="January_last_year">'Report'!$B$10</definedName>
+    <definedName name="Year_to_date_Jul_to_Jan_2026">'Report'!$B$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$E$21</definedName>
@@ -29,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;[Red](#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Roboto"/>
       <sz val="11"/>
@@ -49,6 +49,11 @@
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -110,31 +115,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -647,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -673,7 +681,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -681,128 +689,136 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: $182 per new customer in January: 44 new customers from $8,000 of marketing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>Marketing spend divided by the customers it actually brought in (a customer's first ever job), month by month.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>January 2026</t>
-        </is>
-      </c>
-      <c r="B8" s="6">
-        <f>Workings!B10</f>
-        <v/>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>December $173</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>January last year</t>
-        </is>
-      </c>
-      <c r="B9" s="6">
-        <f>Workings!B18</f>
-        <v/>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>40 new customers from $8,000</t>
+          <t>January 2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>Workings!B10</f>
+        <v/>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>December $173</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>January last year</t>
+        </is>
+      </c>
+      <c r="B10" s="7">
+        <f>Workings!B18</f>
+        <v/>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>40 new customers from $8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Year to date (Jul to Jan 2026)</t>
         </is>
       </c>
-      <c r="B10" s="6">
+      <c r="B11" s="7">
         <f>Workings!B26</f>
         <v/>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>same period last year: not in the data</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Cost to win a customer, by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>44 new customers came from $8,000 of marketing in January, against 45 from $7,800 in December: $182 each, up from $173.</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Worth knowing which channels brought this month's customers in: recording the source of each new customer shows the cost per channel.</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20"/>
+    <row r="21"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-win.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-win.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -843,33 +859,33 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Cost to win a customer, January and December</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Marketing spend ÷ new customers</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
@@ -881,10 +897,10 @@
           <t>Marketing spend (ledger)</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>7800</v>
       </c>
     </row>
@@ -894,24 +910,24 @@
           <t>New customers (first job ever)</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Cost per new customer</t>
         </is>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="14">
         <f>B8/B9</f>
         <v/>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="14">
         <f>C8/C9</f>
         <v/>
       </c>
@@ -919,22 +935,22 @@
     <row r="11"/>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Cost to win a customer, Jan 25</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Marketing spend ÷ new customers</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
@@ -946,7 +962,7 @@
           <t>Marketing spend (ledger)</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="12" t="n">
         <v>8000</v>
       </c>
     </row>
@@ -956,17 +972,17 @@
           <t>New customers (first job ever)</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B17" s="12" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Cost per new customer</t>
         </is>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="14">
         <f>B16/B17</f>
         <v/>
       </c>
@@ -974,22 +990,22 @@
     <row r="19"/>
     <row r="20"/>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Cost to win a customer, FY2026 to date</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Total marketing ÷ total new customers</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Year to date</t>
         </is>
@@ -1001,7 +1017,7 @@
           <t>Marketing, Jul to Jan 2026</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n">
+      <c r="B24" s="12" t="n">
         <v>58200</v>
       </c>
     </row>
@@ -1011,17 +1027,17 @@
           <t>New customers, Jul to Jan 2026</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n">
+      <c r="B25" s="12" t="n">
         <v>255</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>Cost per customer, year to date</t>
         </is>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="14">
         <f>B24/B25</f>
         <v/>
       </c>
@@ -1042,7 +1058,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-win.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-win.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1084,386 +1100,386 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Marketing spend</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>New customers</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Cost per new customer</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>8600</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="12">
         <f>C6/D6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>8400</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="12">
         <f>C7/D7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>7800</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="12">
         <f>C8/D8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="12">
         <f>C9/D9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="12" t="n">
         <v>8600</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="12">
         <f>C10/D10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="12" t="n">
         <v>8400</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="12">
         <f>C11/D11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <v>8400</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="12">
         <f>C12/D12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="12" t="n">
         <v>8400</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="12">
         <f>C13/D13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="12" t="n">
         <v>8400</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="12">
         <f>C14/D14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="12" t="n">
         <v>8400</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="12">
         <f>C15/D15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="12" t="n">
         <v>8400</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="12">
         <f>C16/D16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="12" t="n">
         <v>8600</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="12">
         <f>C17/D17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="12" t="n">
         <v>8600</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="12">
         <f>C18/D18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="12" t="n">
         <v>8400</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="12">
         <f>C19/D19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C20" s="12" t="n">
         <v>7800</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="12">
         <f>C20/D20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C21" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="12">
         <f>C21/D21</f>
         <v/>
       </c>
@@ -1474,7 +1490,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-win.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cost-to-win.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
